--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI31"/>
+  <dimension ref="A1:AI30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>7.98</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3950,27 +3950,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>6.69</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4060,125 +4060,6 @@
         <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46058.875</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>46058</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Cruzeiro</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Coritiba</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M31" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="N31" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" s="3" t="n">
         <v>46058.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>7.98</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>7.98</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G29" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>7.98</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>7.98</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI30"/>
+  <dimension ref="A1:AI29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>7.98</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>7.98</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3831,27 +3831,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>6.69</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3941,125 +3941,6 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>46058.875</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>46058</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Cruzeiro</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Coritiba</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M30" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="N30" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" s="3" t="n">
         <v>46058.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.76</v>
+        <v>2.55</v>
       </c>
       <c r="M19" t="n">
-        <v>3.18</v>
+        <v>2.53</v>
       </c>
       <c r="N19" t="n">
-        <v>4.64</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.55</v>
+        <v>1.76</v>
       </c>
       <c r="M20" t="n">
-        <v>2.53</v>
+        <v>3.18</v>
       </c>
       <c r="N20" t="n">
-        <v>3.2</v>
+        <v>4.64</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G27" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>7.98</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>7.98</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -1858,64 +1858,64 @@
         <v>3.24</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46058.5</v>
@@ -1977,64 +1977,64 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46058.51388888889</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2453,64 +2453,64 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.55</v>
+        <v>1.76</v>
       </c>
       <c r="M19" t="n">
-        <v>2.53</v>
+        <v>3.18</v>
       </c>
       <c r="N19" t="n">
-        <v>3.2</v>
+        <v>4.64</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46058.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.76</v>
+        <v>2.55</v>
       </c>
       <c r="M20" t="n">
-        <v>3.18</v>
+        <v>2.53</v>
       </c>
       <c r="N20" t="n">
-        <v>4.64</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46058.625</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1382,64 +1382,64 @@
         <v>1.65</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46058.45833333334</v>
@@ -1501,46 +1501,46 @@
         <v>7.98</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>7.42</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AC9" t="n">
         <v>1.81</v>
@@ -1549,16 +1549,16 @@
         <v>1.93</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46058.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46058.5</v>
@@ -2334,64 +2334,64 @@
         <v>2.55</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46058.57291666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,40 +2444,40 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O17" t="n">
-        <v>9.5</v>
+        <v>1.7</v>
       </c>
       <c r="P17" t="n">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.45</v>
+        <v>7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="S17" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="T17" t="n">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="U17" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="V17" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -2486,31 +2486,31 @@
         <v>1.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.97</v>
+        <v>2.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.01</v>
+        <v>3.24</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,40 +2563,40 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
         <v>9.5</v>
       </c>
-      <c r="O18" t="n">
-        <v>1.7</v>
-      </c>
       <c r="P18" t="n">
-        <v>2.62</v>
+        <v>2.96</v>
       </c>
       <c r="Q18" t="n">
-        <v>7</v>
+        <v>1.45</v>
       </c>
       <c r="R18" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="T18" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="U18" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="V18" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -2605,31 +2605,31 @@
         <v>1.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.65</v>
+        <v>2.97</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.18</v>
+        <v>1.83</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.24</v>
+        <v>1.01</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.76</v>
+        <v>2.55</v>
       </c>
       <c r="M19" t="n">
-        <v>3.18</v>
+        <v>2.53</v>
       </c>
       <c r="N19" t="n">
-        <v>4.64</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
-        <v>2.42</v>
+        <v>3.57</v>
       </c>
       <c r="P19" t="n">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="S19" t="n">
-        <v>2.33</v>
+        <v>1.98</v>
       </c>
       <c r="T19" t="n">
-        <v>3.32</v>
+        <v>4.3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="V19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.65</v>
+        <v>2.13</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.34</v>
+        <v>3.04</v>
       </c>
       <c r="AB19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF19" t="n">
         <v>1.51</v>
       </c>
-      <c r="AC19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AG19" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.87</v>
+        <v>1.41</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46058.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.55</v>
+        <v>1.76</v>
       </c>
       <c r="M20" t="n">
-        <v>2.53</v>
+        <v>3.18</v>
       </c>
       <c r="N20" t="n">
-        <v>3.2</v>
+        <v>4.64</v>
       </c>
       <c r="O20" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="P20" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="Q20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V20" t="n">
+        <v>9</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC20" t="n">
         <v>4.5</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U20" t="n">
+      <c r="AD20" t="n">
         <v>1.15</v>
       </c>
-      <c r="V20" t="n">
-        <v>11</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AE20" t="n">
-        <v>2.38</v>
+        <v>2.09</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.41</v>
+        <v>1.87</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46058.625</v>
@@ -2929,64 +2929,64 @@
         <v>5.15</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46058.64583333334</v>
@@ -3048,64 +3048,64 @@
         <v>2.14</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46058.70902777778</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>7.98</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.42</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>7.98</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>7.42</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46058.48958333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,40 +2444,40 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
         <v>9.5</v>
       </c>
-      <c r="O17" t="n">
-        <v>1.7</v>
-      </c>
       <c r="P17" t="n">
-        <v>2.62</v>
+        <v>2.96</v>
       </c>
       <c r="Q17" t="n">
-        <v>7</v>
+        <v>1.45</v>
       </c>
       <c r="R17" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="S17" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="T17" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="U17" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="V17" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -2486,31 +2486,31 @@
         <v>1.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.65</v>
+        <v>2.97</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.18</v>
+        <v>1.83</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.24</v>
+        <v>1.01</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,40 +2563,40 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O18" t="n">
-        <v>9.5</v>
+        <v>1.7</v>
       </c>
       <c r="P18" t="n">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.45</v>
+        <v>7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="S18" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="T18" t="n">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="U18" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="V18" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -2605,31 +2605,31 @@
         <v>1.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.97</v>
+        <v>2.65</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.01</v>
+        <v>3.24</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46058.60416666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -3167,64 +3167,64 @@
         <v>3.4</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46058.79166666666</v>
@@ -3286,64 +3286,64 @@
         <v>6.32</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46058.83333333334</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3881,64 +3881,64 @@
         <v>6.69</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46058.89583333334</v>

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>7.98</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>7.42</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>7.98</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.42</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46058.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46058.5</v>
@@ -2215,64 +2215,64 @@
         <v>5.37</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.55</v>
+        <v>1.76</v>
       </c>
       <c r="M19" t="n">
-        <v>2.53</v>
+        <v>3.18</v>
       </c>
       <c r="N19" t="n">
-        <v>3.2</v>
+        <v>4.64</v>
       </c>
       <c r="O19" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="P19" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="Q19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V19" t="n">
+        <v>9</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC19" t="n">
         <v>4.5</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="T19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U19" t="n">
+      <c r="AD19" t="n">
         <v>1.15</v>
       </c>
-      <c r="V19" t="n">
-        <v>11</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AE19" t="n">
-        <v>2.38</v>
+        <v>2.09</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.41</v>
+        <v>1.87</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46058.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.76</v>
+        <v>2.55</v>
       </c>
       <c r="M20" t="n">
-        <v>3.18</v>
+        <v>2.53</v>
       </c>
       <c r="N20" t="n">
-        <v>4.64</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
-        <v>2.42</v>
+        <v>3.57</v>
       </c>
       <c r="P20" t="n">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="S20" t="n">
-        <v>2.33</v>
+        <v>1.98</v>
       </c>
       <c r="T20" t="n">
-        <v>3.32</v>
+        <v>4.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="V20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.65</v>
+        <v>2.13</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.34</v>
+        <v>3.04</v>
       </c>
       <c r="AB20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1.51</v>
       </c>
-      <c r="AC20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AG20" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.87</v>
+        <v>1.41</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46058.625</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>7.98</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.42</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>7.98</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>7.42</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46058.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46058.5</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.76</v>
+        <v>2.55</v>
       </c>
       <c r="M19" t="n">
-        <v>3.18</v>
+        <v>2.53</v>
       </c>
       <c r="N19" t="n">
-        <v>4.64</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
-        <v>2.42</v>
+        <v>3.57</v>
       </c>
       <c r="P19" t="n">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="S19" t="n">
-        <v>2.33</v>
+        <v>1.98</v>
       </c>
       <c r="T19" t="n">
-        <v>3.32</v>
+        <v>4.3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="V19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.65</v>
+        <v>2.13</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.34</v>
+        <v>3.04</v>
       </c>
       <c r="AB19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF19" t="n">
         <v>1.51</v>
       </c>
-      <c r="AC19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AG19" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.87</v>
+        <v>1.41</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46058.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.55</v>
+        <v>1.76</v>
       </c>
       <c r="M20" t="n">
-        <v>2.53</v>
+        <v>3.18</v>
       </c>
       <c r="N20" t="n">
-        <v>3.2</v>
+        <v>4.64</v>
       </c>
       <c r="O20" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="P20" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="Q20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V20" t="n">
+        <v>9</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC20" t="n">
         <v>4.5</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U20" t="n">
+      <c r="AD20" t="n">
         <v>1.15</v>
       </c>
-      <c r="V20" t="n">
-        <v>11</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AE20" t="n">
-        <v>2.38</v>
+        <v>2.09</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.41</v>
+        <v>1.87</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46058.625</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1373,25 +1373,25 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="M8" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="N8" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="O8" t="n">
-        <v>5.04</v>
+        <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
         <v>3.26</v>
@@ -1400,10 +1400,10 @@
         <v>2.45</v>
       </c>
       <c r="U8" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
         <v>1.11</v>
@@ -1412,7 +1412,7 @@
         <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
         <v>3.8</v>
@@ -1427,19 +1427,19 @@
         <v>2.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46058.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46058.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46058.5</v>
@@ -1977,25 +1977,25 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.37</v>
+        <v>5.47</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V13" t="n">
         <v>6.5</v>
@@ -2004,37 +2004,37 @@
         <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46058.51388888889</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.73</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,40 +2444,40 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O17" t="n">
-        <v>9.5</v>
+        <v>1.67</v>
       </c>
       <c r="P17" t="n">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.45</v>
+        <v>7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>3.95</v>
+        <v>3.58</v>
       </c>
       <c r="T17" t="n">
-        <v>1.94</v>
+        <v>2.13</v>
       </c>
       <c r="U17" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="V17" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -2486,31 +2486,31 @@
         <v>1.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.97</v>
+        <v>2.49</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.97</v>
+        <v>1.76</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,40 +2563,40 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.7</v>
+        <v>10.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.62</v>
+        <v>2.96</v>
       </c>
       <c r="Q18" t="n">
-        <v>7</v>
+        <v>1.47</v>
       </c>
       <c r="R18" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>3.94</v>
       </c>
       <c r="T18" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="U18" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="V18" t="n">
-        <v>4.6</v>
+        <v>3.86</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -2605,31 +2605,31 @@
         <v>1.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.65</v>
+        <v>2.97</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.18</v>
+        <v>1.83</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.24</v>
+        <v>1.01</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46058.60416666666</v>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="M23" t="n">
-        <v>3.17</v>
+        <v>3.09</v>
       </c>
       <c r="N23" t="n">
         <v>3.4</v>
@@ -3170,10 +3170,10 @@
         <v>2.75</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.19</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
         <v>1.46</v>
@@ -3197,10 +3197,10 @@
         <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="AA23" t="n">
         <v>2</v>
@@ -3212,16 +3212,16 @@
         <v>4</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
         <v>1.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
         <v>1.67</v>
@@ -3277,70 +3277,70 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="M24" t="n">
-        <v>4.32</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>6.32</v>
+        <v>5.4</v>
       </c>
       <c r="O24" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="P24" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.82</v>
+        <v>5.79</v>
       </c>
       <c r="R24" t="n">
         <v>1.41</v>
       </c>
       <c r="S24" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="T24" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V24" t="n">
-        <v>7.2</v>
+        <v>6.95</v>
       </c>
       <c r="W24" t="n">
         <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
         <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AA24" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB24" t="n">
         <v>1.85</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="AD24" t="n">
         <v>1.28</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH24" t="n">
         <v>2.15</v>
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="M29" t="n">
-        <v>4.32</v>
+        <v>4.22</v>
       </c>
       <c r="N29" t="n">
-        <v>6.69</v>
+        <v>7.7</v>
       </c>
       <c r="O29" t="n">
         <v>2</v>
@@ -3893,10 +3893,10 @@
         <v>1.41</v>
       </c>
       <c r="S29" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="T29" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U29" t="n">
         <v>1.36</v>
@@ -3905,40 +3905,40 @@
         <v>6.75</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y29" t="n">
         <v>1.34</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="AF29" t="n">
         <v>1.65</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46058.89583333334</v>

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -1385,16 +1385,16 @@
         <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>3.26</v>
+        <v>2.96</v>
       </c>
       <c r="T8" t="n">
         <v>2.45</v>
@@ -1412,13 +1412,13 @@
         <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.8</v>
+        <v>3.87</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AB8" t="n">
         <v>2.02</v>
@@ -1427,19 +1427,19 @@
         <v>2.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AG8" t="n">
         <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46058.45833333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>7.98</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.42</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46058.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46058.5</v>
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="N14" t="n">
-        <v>5.37</v>
+        <v>4.59</v>
       </c>
       <c r="O14" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.73</v>
+        <v>5.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="T14" t="n">
-        <v>2.99</v>
+        <v>3.17</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V14" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD14" t="n">
         <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2325,22 +2325,22 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="P16" t="n">
         <v>2.35</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.29</v>
-      </c>
       <c r="Q16" t="n">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="R16" t="n">
         <v>1.22</v>
@@ -2352,7 +2352,7 @@
         <v>2.07</v>
       </c>
       <c r="U16" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="V16" t="n">
         <v>4.33</v>
@@ -2364,19 +2364,19 @@
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z16" t="n">
         <v>5.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AD16" t="n">
         <v>1.71</v>
@@ -2385,13 +2385,13 @@
         <v>1.36</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46058.57291666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,40 +2444,40 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.67</v>
+        <v>10.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="Q17" t="n">
-        <v>7</v>
+        <v>1.47</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="S17" t="n">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="T17" t="n">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="U17" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="V17" t="n">
-        <v>4.5</v>
+        <v>3.86</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -2486,31 +2486,31 @@
         <v>1.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.49</v>
+        <v>2.97</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,40 +2563,40 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O18" t="n">
-        <v>10.5</v>
+        <v>1.67</v>
       </c>
       <c r="P18" t="n">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.47</v>
+        <v>7</v>
       </c>
       <c r="R18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.14</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V18" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.18</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -2605,31 +2605,31 @@
         <v>1.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.3</v>
+        <v>5.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.97</v>
+        <v>2.49</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.98</v>
+        <v>1.76</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.72</v>
+        <v>1.94</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2682,28 +2682,28 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="M19" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="N19" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="P19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="R19" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="S19" t="n">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="T19" t="n">
         <v>4.3</v>
@@ -2715,16 +2715,16 @@
         <v>11</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
         <v>1.11</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AA19" t="n">
         <v>3.04</v>
@@ -2745,7 +2745,7 @@
         <v>1.51</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AH19" t="n">
         <v>1.41</v>
@@ -2801,28 +2801,28 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="M20" t="n">
-        <v>3.18</v>
+        <v>3.04</v>
       </c>
       <c r="N20" t="n">
-        <v>4.64</v>
+        <v>4.59</v>
       </c>
       <c r="O20" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="P20" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="Q20" t="n">
         <v>5.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="S20" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="T20" t="n">
         <v>3.32</v>
@@ -2834,40 +2834,40 @@
         <v>9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Z20" t="n">
         <v>2.65</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD20" t="n">
         <v>1.15</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46058.625</v>
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>3.49</v>
       </c>
       <c r="N21" t="n">
-        <v>5.15</v>
+        <v>4.69</v>
       </c>
       <c r="O21" t="n">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="P21" t="n">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.56</v>
+        <v>4.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S21" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="V21" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46058.64583333334</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -1977,19 +1977,19 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="P13" t="n">
         <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.47</v>
+        <v>5.32</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T13" t="n">
         <v>2.4</v>
@@ -2010,19 +2010,19 @@
         <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE13" t="n">
         <v>1.75</v>
@@ -2034,7 +2034,7 @@
         <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46058.51388888889</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2459,7 +2459,7 @@
         <v>2.96</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R17" t="n">
         <v>1.14</v>
@@ -2468,7 +2468,7 @@
         <v>3.94</v>
       </c>
       <c r="T17" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="U17" t="n">
         <v>1.76</v>
@@ -2507,7 +2507,7 @@
         <v>1.72</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AH17" t="n">
         <v>1.01</v>
@@ -2563,25 +2563,25 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="M18" t="n">
-        <v>5.25</v>
+        <v>6.44</v>
       </c>
       <c r="N18" t="n">
-        <v>9.5</v>
+        <v>9.59</v>
       </c>
       <c r="O18" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="P18" t="n">
         <v>2.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>7</v>
+        <v>7.38</v>
       </c>
       <c r="R18" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S18" t="n">
         <v>3.58</v>
@@ -2608,10 +2608,10 @@
         <v>5.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="AC18" t="n">
         <v>2.12</v>
@@ -2626,10 +2626,10 @@
         <v>1.94</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.35</v>
+        <v>3.24</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.54</v>
+        <v>1.75</v>
       </c>
       <c r="M19" t="n">
-        <v>2.56</v>
+        <v>3.04</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>4.59</v>
       </c>
       <c r="O19" t="n">
-        <v>3.54</v>
+        <v>2.52</v>
       </c>
       <c r="P19" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.69</v>
+        <v>1.52</v>
       </c>
       <c r="S19" t="n">
-        <v>2.11</v>
+        <v>2.29</v>
       </c>
       <c r="T19" t="n">
-        <v>4.3</v>
+        <v>3.32</v>
       </c>
       <c r="U19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V19" t="n">
+        <v>9</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.15</v>
       </c>
-      <c r="V19" t="n">
-        <v>11</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AE19" t="n">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.41</v>
+        <v>1.99</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46058.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.75</v>
+        <v>2.54</v>
       </c>
       <c r="M20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V20" t="n">
+        <v>11</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA20" t="n">
         <v>3.04</v>
       </c>
-      <c r="N20" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V20" t="n">
-        <v>9</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X20" t="n">
+      <c r="AB20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AA20" t="n">
+      <c r="AE20" t="n">
         <v>2.38</v>
       </c>
-      <c r="AB20" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.06</v>
-      </c>
       <c r="AF20" t="n">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.99</v>
+        <v>1.41</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46058.625</v>
@@ -3039,28 +3039,28 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.15</v>
+        <v>3.39</v>
       </c>
       <c r="M22" t="n">
         <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
-        <v>4.06</v>
+        <v>3.75</v>
       </c>
       <c r="P22" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="R22" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="T22" t="n">
         <v>2.98</v>
@@ -3075,34 +3075,34 @@
         <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.51</v>
+        <v>2.95</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
         <v>1.3</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46058.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46058.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46058.54166666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46058.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46058.5</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,40 +2444,40 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>6.44</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>9.59</v>
       </c>
       <c r="O17" t="n">
-        <v>10.5</v>
+        <v>1.69</v>
       </c>
       <c r="P17" t="n">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.46</v>
+        <v>7.38</v>
       </c>
       <c r="R17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W17" t="n">
         <v>1.14</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V17" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.18</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -2486,31 +2486,31 @@
         <v>1.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.3</v>
+        <v>5.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.97</v>
+        <v>2.63</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.98</v>
+        <v>1.76</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.72</v>
+        <v>1.94</v>
       </c>
       <c r="AG17" t="n">
-        <v>5</v>
+        <v>1.09</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.01</v>
+        <v>3.24</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,40 +2563,40 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>6.44</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>9.59</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.69</v>
+        <v>10.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.38</v>
+        <v>1.46</v>
       </c>
       <c r="R18" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="S18" t="n">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="T18" t="n">
-        <v>2.13</v>
+        <v>1.94</v>
       </c>
       <c r="U18" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="V18" t="n">
-        <v>4.5</v>
+        <v>3.86</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -2605,31 +2605,31 @@
         <v>1.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.63</v>
+        <v>2.97</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.09</v>
+        <v>5</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.24</v>
+        <v>1.01</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.75</v>
+        <v>2.54</v>
       </c>
       <c r="M19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V19" t="n">
+        <v>11</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA19" t="n">
         <v>3.04</v>
       </c>
-      <c r="N19" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V19" t="n">
-        <v>9</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X19" t="n">
+      <c r="AB19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AA19" t="n">
+      <c r="AE19" t="n">
         <v>2.38</v>
       </c>
-      <c r="AB19" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.06</v>
-      </c>
       <c r="AF19" t="n">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.99</v>
+        <v>1.41</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46058.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.54</v>
+        <v>1.75</v>
       </c>
       <c r="M20" t="n">
-        <v>2.56</v>
+        <v>3.04</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>4.59</v>
       </c>
       <c r="O20" t="n">
-        <v>3.54</v>
+        <v>2.52</v>
       </c>
       <c r="P20" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.69</v>
+        <v>1.52</v>
       </c>
       <c r="S20" t="n">
-        <v>2.11</v>
+        <v>2.29</v>
       </c>
       <c r="T20" t="n">
-        <v>4.3</v>
+        <v>3.32</v>
       </c>
       <c r="U20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V20" t="n">
+        <v>9</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.15</v>
       </c>
-      <c r="V20" t="n">
-        <v>11</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AE20" t="n">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.41</v>
+        <v>1.99</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46058.625</v>
@@ -3042,10 +3042,10 @@
         <v>3.39</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
         <v>3.75</v>
@@ -3057,13 +3057,13 @@
         <v>2.63</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
         <v>2.69</v>
       </c>
       <c r="T22" t="n">
-        <v>2.98</v>
+        <v>2.85</v>
       </c>
       <c r="U22" t="n">
         <v>1.36</v>
@@ -3075,7 +3075,7 @@
         <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
         <v>1.3</v>
@@ -3084,13 +3084,13 @@
         <v>3.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="AD22" t="n">
         <v>1.25</v>
@@ -3102,7 +3102,7 @@
         <v>1.95</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
         <v>1.3</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1730,19 +1730,19 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="N11" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
         <v>3.32</v>
       </c>
       <c r="P11" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="Q11" t="n">
         <v>4.44</v>
@@ -1754,7 +1754,7 @@
         <v>2.1</v>
       </c>
       <c r="T11" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="U11" t="n">
         <v>1.17</v>
@@ -1766,7 +1766,7 @@
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Y11" t="n">
         <v>1.57</v>
@@ -1781,16 +1781,16 @@
         <v>1.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.65</v>
+        <v>5.7</v>
       </c>
       <c r="AD11" t="n">
         <v>1.08</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AG11" t="n">
         <v>1.36</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2682,34 +2682,34 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="M19" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
-        <v>3.54</v>
+        <v>3.64</v>
       </c>
       <c r="P19" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="R19" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="S19" t="n">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="T19" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="U19" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="V19" t="n">
         <v>11</v>
@@ -2718,19 +2718,19 @@
         <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Y19" t="n">
         <v>1.7</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AC19" t="n">
         <v>6.5</v>
@@ -2745,10 +2745,10 @@
         <v>1.51</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46058.625</v>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="M20" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>4.59</v>
+        <v>4</v>
       </c>
       <c r="O20" t="n">
         <v>2.52</v>
@@ -2816,13 +2816,13 @@
         <v>1.88</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.4</v>
+        <v>5.67</v>
       </c>
       <c r="R20" t="n">
         <v>1.52</v>
       </c>
       <c r="S20" t="n">
-        <v>2.29</v>
+        <v>2.54</v>
       </c>
       <c r="T20" t="n">
         <v>3.32</v>
@@ -2831,10 +2831,10 @@
         <v>1.26</v>
       </c>
       <c r="V20" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
         <v>1.05</v>
@@ -2846,28 +2846,28 @@
         <v>2.65</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="AC20" t="n">
         <v>4.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46058.625</v>
@@ -3158,22 +3158,22 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
         <v>3.09</v>
       </c>
       <c r="N23" t="n">
-        <v>3.4</v>
+        <v>3.66</v>
       </c>
       <c r="O23" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="P23" t="n">
         <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="R23" t="n">
         <v>1.46</v>
@@ -3182,7 +3182,7 @@
         <v>2.53</v>
       </c>
       <c r="T23" t="n">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="U23" t="n">
         <v>1.36</v>
@@ -3200,28 +3200,28 @@
         <v>1.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="AA23" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AC23" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AD23" t="n">
         <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
         <v>1.67</v>
@@ -3277,25 +3277,25 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N24" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O24" t="n">
         <v>2.15</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.79</v>
+        <v>5.75</v>
       </c>
       <c r="R24" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
         <v>2.65</v>
@@ -3316,7 +3316,7 @@
         <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
         <v>3.25</v>
@@ -3325,13 +3325,13 @@
         <v>1.95</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC24" t="n">
         <v>3.49</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE24" t="n">
         <v>1.85</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3872,19 +3872,19 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="M29" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="N29" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="O29" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q29" t="n">
         <v>6.5</v>
@@ -3896,7 +3896,7 @@
         <v>2.69</v>
       </c>
       <c r="T29" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U29" t="n">
         <v>1.36</v>
@@ -3911,13 +3911,13 @@
         <v>1.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z29" t="n">
         <v>3.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AB29" t="n">
         <v>1.75</v>
@@ -3929,10 +3929,10 @@
         <v>1.25</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG29" t="n">
         <v>1.22</v>

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -1730,25 +1730,25 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="M11" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.44</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="S11" t="n">
         <v>2.1</v>
@@ -1766,13 +1766,13 @@
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
         <v>1.57</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AA11" t="n">
         <v>2.87</v>
@@ -1790,13 +1790,13 @@
         <v>2.21</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46058.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,40 +2444,40 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>6.44</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>9.59</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.69</v>
+        <v>10.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.38</v>
+        <v>1.46</v>
       </c>
       <c r="R17" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="S17" t="n">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="T17" t="n">
-        <v>2.13</v>
+        <v>1.94</v>
       </c>
       <c r="U17" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="V17" t="n">
-        <v>4.5</v>
+        <v>3.86</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -2486,31 +2486,31 @@
         <v>1.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.63</v>
+        <v>2.97</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.09</v>
+        <v>5</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.24</v>
+        <v>1.01</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,40 +2563,40 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>6.44</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>9.59</v>
       </c>
       <c r="O18" t="n">
-        <v>10.5</v>
+        <v>1.69</v>
       </c>
       <c r="P18" t="n">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.46</v>
+        <v>7.38</v>
       </c>
       <c r="R18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.14</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V18" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.18</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -2605,31 +2605,31 @@
         <v>1.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.3</v>
+        <v>5.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.97</v>
+        <v>2.63</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.98</v>
+        <v>1.76</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.72</v>
+        <v>1.94</v>
       </c>
       <c r="AG18" t="n">
-        <v>5</v>
+        <v>1.09</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.01</v>
+        <v>3.24</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2682,22 +2682,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="M19" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="O19" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.25</v>
+        <v>4.62</v>
       </c>
       <c r="R19" t="n">
         <v>1.76</v>
@@ -2706,13 +2706,13 @@
         <v>1.94</v>
       </c>
       <c r="T19" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="U19" t="n">
         <v>1.14</v>
       </c>
       <c r="V19" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="W19" t="n">
         <v>1.02</v>
@@ -2724,13 +2724,13 @@
         <v>1.7</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AA19" t="n">
         <v>3.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AC19" t="n">
         <v>6.5</v>
@@ -2745,7 +2745,7 @@
         <v>1.51</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AH19" t="n">
         <v>1.4</v>
@@ -2801,37 +2801,37 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="M20" t="n">
         <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O20" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="P20" t="n">
         <v>1.88</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.67</v>
+        <v>5.4</v>
       </c>
       <c r="R20" t="n">
         <v>1.52</v>
       </c>
       <c r="S20" t="n">
-        <v>2.54</v>
+        <v>2.29</v>
       </c>
       <c r="T20" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="U20" t="n">
         <v>1.26</v>
       </c>
       <c r="V20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W20" t="n">
         <v>1.01</v>
@@ -2843,31 +2843,31 @@
         <v>1.45</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46058.625</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G27" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46058.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46058.5</v>
@@ -3039,34 +3039,34 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="M22" t="n">
         <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
         <v>3.75</v>
       </c>
       <c r="P22" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
         <v>2.69</v>
       </c>
       <c r="T22" t="n">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="U22" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V22" t="n">
         <v>7.1</v>
@@ -3075,16 +3075,16 @@
         <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AB22" t="n">
         <v>1.75</v>
@@ -3093,7 +3093,7 @@
         <v>3.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE22" t="n">
         <v>1.75</v>
@@ -3102,7 +3102,7 @@
         <v>1.95</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
         <v>1.3</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46058.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46058.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46058.54166666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G27" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1977,52 +1977,52 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.32</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S13" t="n">
         <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="U13" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V13" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="W13" t="n">
         <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z13" t="n">
         <v>3.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE13" t="n">
         <v>1.75</v>
@@ -2034,7 +2034,7 @@
         <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46058.51388888889</v>
@@ -2209,67 +2209,67 @@
         <v>1.68</v>
       </c>
       <c r="M15" t="n">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="N15" t="n">
-        <v>4.59</v>
+        <v>4.05</v>
       </c>
       <c r="O15" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="P15" t="n">
         <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="T15" t="n">
-        <v>3.17</v>
+        <v>2.85</v>
       </c>
       <c r="U15" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AF15" t="n">
         <v>1.82</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AH15" t="n">
         <v>1.95</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O17" t="n">
-        <v>10.5</v>
+        <v>1.53</v>
       </c>
       <c r="P17" t="n">
-        <v>2.96</v>
+        <v>3.17</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.46</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R17" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="S17" t="n">
-        <v>3.94</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="U17" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V17" t="n">
-        <v>3.86</v>
+        <v>4.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.1</v>
       </c>
-      <c r="Z17" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>5</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>6.44</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>9.59</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.69</v>
+        <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>2.75</v>
+        <v>3.44</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.38</v>
+        <v>1.44</v>
       </c>
       <c r="R18" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>3.58</v>
+        <v>4.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="U18" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="V18" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
         <v>1.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.24</v>
+        <v>1.03</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2920,37 +2920,37 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="M21" t="n">
-        <v>3.49</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>4.69</v>
+        <v>4.2</v>
       </c>
       <c r="O21" t="n">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="P21" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="T21" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="U21" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="V21" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="W21" t="n">
         <v>1.02</v>
@@ -2962,31 +2962,31 @@
         <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD21" t="n">
         <v>1.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AF21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.87</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.95</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46058.64583333334</v>
@@ -3158,22 +3158,22 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="M23" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="N23" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="O23" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="P23" t="n">
         <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="R23" t="n">
         <v>1.46</v>
@@ -3182,46 +3182,46 @@
         <v>2.53</v>
       </c>
       <c r="T23" t="n">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="U23" t="n">
         <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>8</v>
+        <v>6.75</v>
       </c>
       <c r="W23" t="n">
         <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z23" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
         <v>1.67</v>
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M24" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="O24" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="P24" t="n">
-        <v>2.07</v>
+        <v>2.31</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.75</v>
+        <v>6.03</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="T24" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="U24" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V24" t="n">
-        <v>6.95</v>
+        <v>6.5</v>
       </c>
       <c r="W24" t="n">
         <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
         <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="AA24" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF24" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46058.83333333334</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3872,28 +3872,28 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="M29" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="N29" t="n">
         <v>7.5</v>
       </c>
       <c r="O29" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="P29" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="R29" t="n">
         <v>1.41</v>
       </c>
       <c r="S29" t="n">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="T29" t="n">
         <v>2.88</v>
@@ -3902,25 +3902,25 @@
         <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="W29" t="n">
         <v>1.04</v>
       </c>
       <c r="X29" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AC29" t="n">
         <v>3.5</v>
@@ -3929,13 +3929,13 @@
         <v>1.25</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH29" t="n">
         <v>2.63</v>

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="O8" t="n">
         <v>5</v>
@@ -1388,46 +1388,46 @@
         <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="U8" t="n">
         <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.87</v>
+        <v>3.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE8" t="n">
         <v>1.7</v>
@@ -1439,7 +1439,7 @@
         <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46058.45833333334</v>
@@ -1492,64 +1492,64 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="M9" t="n">
         <v>6.5</v>
       </c>
       <c r="N9" t="n">
-        <v>10</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="P9" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
         <v>7.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="S9" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U9" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="V9" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AF9" t="n">
         <v>2.22</v>
@@ -1730,34 +1730,34 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="P11" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q11" t="n">
         <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="T11" t="n">
-        <v>3.96</v>
+        <v>4.15</v>
       </c>
       <c r="U11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="V11" t="n">
         <v>13</v>
@@ -1766,37 +1766,37 @@
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.7</v>
+        <v>6.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG11" t="n">
         <v>1.44</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46058.5</v>
@@ -1995,13 +1995,13 @@
         <v>2.6</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V13" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
         <v>1</v>
@@ -2034,7 +2034,7 @@
         <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46058.51388888889</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>4.05</v>
+        <v>4.79</v>
       </c>
       <c r="O15" t="n">
         <v>2.3</v>
@@ -2221,7 +2221,7 @@
         <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="R15" t="n">
         <v>1.39</v>
@@ -2236,16 +2236,16 @@
         <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
         <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
         <v>3</v>
@@ -2254,7 +2254,7 @@
         <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AC15" t="n">
         <v>3.28</v>
@@ -2263,10 +2263,10 @@
         <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
         <v>1.16</v>
@@ -2325,28 +2325,28 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.91</v>
+        <v>2.25</v>
       </c>
       <c r="M16" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="O16" t="n">
-        <v>3.49</v>
+        <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.61</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="T16" t="n">
         <v>2.07</v>
@@ -2355,28 +2355,28 @@
         <v>1.67</v>
       </c>
       <c r="V16" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="W16" t="n">
         <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
         <v>1.71</v>
@@ -2388,10 +2388,10 @@
         <v>2.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46058.57291666666</v>
@@ -2444,16 +2444,16 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="M17" t="n">
         <v>6.65</v>
       </c>
       <c r="N17" t="n">
-        <v>15</v>
+        <v>10.6</v>
       </c>
       <c r="O17" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="P17" t="n">
         <v>3.17</v>
@@ -2462,19 +2462,19 @@
         <v>8.699999999999999</v>
       </c>
       <c r="R17" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="T17" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U17" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="V17" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="W17" t="n">
         <v>1.17</v>
@@ -2492,7 +2492,7 @@
         <v>1.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AC17" t="n">
         <v>1.93</v>
@@ -2578,10 +2578,10 @@
         <v>3.44</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="S18" t="n">
         <v>4.75</v>
@@ -2611,7 +2611,7 @@
         <v>1.31</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AC18" t="n">
         <v>1.93</v>
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="M19" t="n">
         <v>2.6</v>
       </c>
       <c r="N19" t="n">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="O19" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
         <v>1.72</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.62</v>
+        <v>4.67</v>
       </c>
       <c r="R19" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="S19" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="T19" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U19" t="n">
         <v>1.14</v>
       </c>
       <c r="V19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W19" t="n">
         <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AC19" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="AD19" t="n">
         <v>1.05</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46058.625</v>
@@ -2801,37 +2801,37 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="N20" t="n">
-        <v>4.3</v>
+        <v>4.89</v>
       </c>
       <c r="O20" t="n">
         <v>2.5</v>
       </c>
       <c r="P20" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="R20" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S20" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="T20" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="U20" t="n">
         <v>1.26</v>
       </c>
       <c r="V20" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="W20" t="n">
         <v>1.01</v>
@@ -2843,25 +2843,25 @@
         <v>1.45</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AG20" t="n">
         <v>1.14</v>
@@ -2920,7 +2920,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="M21" t="n">
         <v>3.35</v>
@@ -2938,7 +2938,7 @@
         <v>4.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
         <v>2.65</v>
@@ -2956,7 +2956,7 @@
         <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
         <v>1.33</v>
@@ -2971,10 +2971,10 @@
         <v>1.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE21" t="n">
         <v>1.95</v>
@@ -2986,7 +2986,7 @@
         <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46058.64583333334</v>
@@ -3039,22 +3039,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
         <v>3.75</v>
       </c>
       <c r="P22" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="R22" t="n">
         <v>1.36</v>
@@ -3066,7 +3066,7 @@
         <v>2.55</v>
       </c>
       <c r="U22" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="V22" t="n">
         <v>7.1</v>
@@ -3078,7 +3078,7 @@
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z22" t="n">
         <v>3.2</v>
@@ -3105,7 +3105,7 @@
         <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46058.70902777778</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -1391,16 +1391,16 @@
         <v>2.22</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="T8" t="n">
         <v>2.53</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V8" t="n">
         <v>6.1</v>
@@ -1409,7 +1409,7 @@
         <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
         <v>1.24</v>
@@ -1427,7 +1427,7 @@
         <v>2.74</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
         <v>1.7</v>
@@ -1436,10 +1436,10 @@
         <v>2.05</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46058.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46058.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46058.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.7</v>
+        <v>1.65</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N14" t="n">
-        <v>1.74</v>
+        <v>4.79</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.65</v>
+        <v>3.7</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>4.79</v>
+        <v>1.74</v>
       </c>
       <c r="O15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2682,34 +2682,34 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="M19" t="n">
         <v>2.6</v>
       </c>
       <c r="N19" t="n">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>3.47</v>
       </c>
       <c r="P19" t="n">
         <v>1.72</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.67</v>
+        <v>4.38</v>
       </c>
       <c r="R19" t="n">
         <v>1.68</v>
       </c>
       <c r="S19" t="n">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="V19" t="n">
         <v>13</v>
@@ -2721,34 +2721,34 @@
         <v>1.11</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46058.625</v>
@@ -2810,7 +2810,7 @@
         <v>4.89</v>
       </c>
       <c r="O20" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="P20" t="n">
         <v>1.89</v>
@@ -2819,7 +2819,7 @@
         <v>5.2</v>
       </c>
       <c r="R20" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="S20" t="n">
         <v>2.31</v>
@@ -2831,16 +2831,16 @@
         <v>1.26</v>
       </c>
       <c r="V20" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W20" t="n">
         <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z20" t="n">
         <v>2.75</v>
@@ -2852,7 +2852,7 @@
         <v>1.58</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.15</v>
+        <v>4.38</v>
       </c>
       <c r="AD20" t="n">
         <v>1.2</v>
@@ -2864,7 +2864,7 @@
         <v>1.71</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AH20" t="n">
         <v>2</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46058.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46058.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.65</v>
+        <v>3.7</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>4.79</v>
+        <v>1.74</v>
       </c>
       <c r="O14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.7</v>
+        <v>1.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>1.74</v>
+        <v>4.79</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.57</v>
+        <v>10</v>
       </c>
       <c r="P17" t="n">
-        <v>3.17</v>
+        <v>3.44</v>
       </c>
       <c r="Q17" t="n">
-        <v>8.699999999999999</v>
+        <v>1.53</v>
       </c>
       <c r="R17" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="S17" t="n">
-        <v>4.05</v>
+        <v>4.75</v>
       </c>
       <c r="T17" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="U17" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="V17" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="W17" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z17" t="n">
         <v>6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AC17" t="n">
         <v>1.93</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="O18" t="n">
-        <v>10</v>
+        <v>1.57</v>
       </c>
       <c r="P18" t="n">
-        <v>3.44</v>
+        <v>3.17</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.53</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R18" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="S18" t="n">
-        <v>4.75</v>
+        <v>4.05</v>
       </c>
       <c r="T18" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="U18" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="V18" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="W18" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z18" t="n">
         <v>6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AC18" t="n">
         <v>1.93</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF18" t="n">
         <v>1.83</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AG18" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.34</v>
+        <v>1.74</v>
       </c>
       <c r="M19" t="n">
-        <v>2.6</v>
+        <v>3.12</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>4.89</v>
       </c>
       <c r="O19" t="n">
-        <v>3.47</v>
+        <v>2.45</v>
       </c>
       <c r="P19" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="Q19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V19" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC19" t="n">
         <v>4.38</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="T19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="V19" t="n">
-        <v>13</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X19" t="n">
+      <c r="AD19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.11</v>
       </c>
-      <c r="Y19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46058.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.74</v>
+        <v>2.34</v>
       </c>
       <c r="M20" t="n">
-        <v>3.12</v>
+        <v>2.6</v>
       </c>
       <c r="N20" t="n">
-        <v>4.89</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
-        <v>2.45</v>
+        <v>3.47</v>
       </c>
       <c r="P20" t="n">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.2</v>
+        <v>4.38</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="S20" t="n">
-        <v>2.31</v>
+        <v>2.11</v>
       </c>
       <c r="T20" t="n">
-        <v>3.32</v>
+        <v>4.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="V20" t="n">
-        <v>8.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.08</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AE20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AH20" t="n">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46058.625</v>
@@ -3039,25 +3039,25 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P22" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.63</v>
+        <v>2.85</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
         <v>2.69</v>
@@ -3066,7 +3066,7 @@
         <v>2.55</v>
       </c>
       <c r="U22" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="V22" t="n">
         <v>7.1</v>
@@ -3081,7 +3081,7 @@
         <v>1.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA22" t="n">
         <v>2.02</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.6</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>4.35</v>
       </c>
       <c r="N6" t="n">
-        <v>1.75</v>
+        <v>6.1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.35</v>
+        <v>3.6</v>
       </c>
       <c r="M7" t="n">
-        <v>4.35</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>6.1</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1730,16 +1730,16 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="P11" t="n">
         <v>1.71</v>
@@ -1751,16 +1751,16 @@
         <v>1.68</v>
       </c>
       <c r="S11" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="T11" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="V11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W11" t="n">
         <v>1.02</v>
@@ -1775,10 +1775,10 @@
         <v>2.14</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AC11" t="n">
         <v>6.2</v>
@@ -1787,16 +1787,16 @@
         <v>1.06</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG11" t="n">
         <v>1.37</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46058.5</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.74</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.48</v>
-      </c>
       <c r="S19" t="n">
-        <v>2.31</v>
+        <v>1.97</v>
       </c>
       <c r="T19" t="n">
-        <v>3.32</v>
+        <v>4.3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="V19" t="n">
-        <v>8.699999999999999</v>
+        <v>11</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.75</v>
+        <v>2.08</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.24</v>
+        <v>3.04</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.38</v>
+        <v>6.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46058.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.34</v>
+        <v>1.73</v>
       </c>
       <c r="M20" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
-        <v>3.47</v>
+        <v>2.45</v>
       </c>
       <c r="P20" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.38</v>
+        <v>5.2</v>
       </c>
       <c r="R20" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="S20" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE20" t="n">
         <v>2.11</v>
       </c>
-      <c r="T20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="V20" t="n">
-        <v>13</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X20" t="n">
+      <c r="AF20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.11</v>
       </c>
-      <c r="Y20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46058.625</v>
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="N23" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="O23" t="n">
         <v>2.8</v>
@@ -3173,7 +3173,7 @@
         <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="R23" t="n">
         <v>1.46</v>
@@ -3197,34 +3197,34 @@
         <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.54</v>
+        <v>3.24</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AF23" t="n">
         <v>1.91</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46058.79166666666</v>
@@ -3280,25 +3280,25 @@
         <v>1.67</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="N24" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="O24" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="P24" t="n">
-        <v>2.31</v>
+        <v>2.09</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.03</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S24" t="n">
-        <v>2.75</v>
+        <v>2.98</v>
       </c>
       <c r="T24" t="n">
         <v>2.81</v>
@@ -3307,25 +3307,25 @@
         <v>1.38</v>
       </c>
       <c r="V24" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="W24" t="n">
         <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
         <v>3.4</v>
@@ -3337,10 +3337,10 @@
         <v>1.95</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AH24" t="n">
         <v>2.2</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3872,55 +3872,55 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="M29" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="N29" t="n">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="O29" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="P29" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="R29" t="n">
         <v>1.41</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="T29" t="n">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V29" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA29" t="n">
         <v>2.04</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC29" t="n">
         <v>3.5</v>
@@ -3929,13 +3929,13 @@
         <v>1.25</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH29" t="n">
         <v>2.63</v>

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N8" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="P8" t="n">
         <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="R8" t="n">
         <v>1.32</v>
@@ -1400,7 +1400,7 @@
         <v>2.53</v>
       </c>
       <c r="U8" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="V8" t="n">
         <v>6.1</v>
@@ -1436,10 +1436,10 @@
         <v>2.05</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.05</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46058.45833333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>8.960000000000001</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="M11" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
         <v>3.42</v>
@@ -1760,25 +1760,25 @@
         <v>1.16</v>
       </c>
       <c r="V11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W11" t="n">
         <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Y11" t="n">
         <v>1.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AA11" t="n">
         <v>2.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AC11" t="n">
         <v>6.2</v>
@@ -1983,49 +1983,49 @@
         <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>4.68</v>
       </c>
       <c r="R13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
         <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="U13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V13" t="n">
         <v>6.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
         <v>2.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AF13" t="n">
         <v>1.91</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.7</v>
+        <v>1.65</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N14" t="n">
-        <v>1.74</v>
+        <v>4.79</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.65</v>
+        <v>3.7</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>4.79</v>
+        <v>1.74</v>
       </c>
       <c r="O15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2456,61 +2456,61 @@
         <v>10</v>
       </c>
       <c r="P17" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="R17" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="T17" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U17" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="V17" t="n">
-        <v>3.9</v>
+        <v>3.96</v>
       </c>
       <c r="W17" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z17" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AB17" t="n">
         <v>2.88</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG17" t="n">
         <v>1.08</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2566,58 +2566,58 @@
         <v>1.14</v>
       </c>
       <c r="M18" t="n">
-        <v>6.65</v>
+        <v>6</v>
       </c>
       <c r="N18" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="P18" t="n">
-        <v>3.17</v>
+        <v>2.83</v>
       </c>
       <c r="Q18" t="n">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="R18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.16</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.17</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AB18" t="n">
         <v>2.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AE18" t="n">
         <v>1.85</v>
@@ -2682,34 +2682,34 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="M19" t="n">
         <v>2.6</v>
       </c>
       <c r="N19" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="O19" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
         <v>1.66</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.67</v>
+        <v>4.62</v>
       </c>
       <c r="R19" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="S19" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="T19" t="n">
         <v>4.3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="V19" t="n">
         <v>11</v>
@@ -2718,13 +2718,13 @@
         <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Y19" t="n">
         <v>1.69</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AA19" t="n">
         <v>3.04</v>
@@ -2745,10 +2745,10 @@
         <v>1.51</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46058.625</v>
@@ -2801,37 +2801,37 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="M20" t="n">
         <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="P20" t="n">
         <v>1.89</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.2</v>
+        <v>5.76</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S20" t="n">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="T20" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="U20" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W20" t="n">
         <v>1.01</v>
@@ -3039,34 +3039,34 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="O22" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P22" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
         <v>2.69</v>
       </c>
       <c r="T22" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="U22" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="V22" t="n">
         <v>7.1</v>
@@ -3078,10 +3078,10 @@
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="AA22" t="n">
         <v>2.02</v>
@@ -3090,10 +3090,10 @@
         <v>1.75</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE22" t="n">
         <v>1.75</v>
@@ -3102,10 +3102,10 @@
         <v>1.95</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46058.70902777778</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G26" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46058.375</v>
@@ -1016,49 +1016,49 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="M5" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="N5" t="n">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA5" t="n">
         <v>3</v>
@@ -1067,22 +1067,22 @@
         <v>1.36</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46058.41666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.35</v>
+        <v>3.6</v>
       </c>
       <c r="M6" t="n">
-        <v>4.35</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>6.1</v>
+        <v>1.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.6</v>
+        <v>1.35</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>4.35</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>6.1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="M8" t="n">
         <v>3.75</v>
@@ -1388,7 +1388,7 @@
         <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="R8" t="n">
         <v>1.32</v>
@@ -1403,37 +1403,37 @@
         <v>1.43</v>
       </c>
       <c r="V8" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
         <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.9</v>
+        <v>3.74</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB8" t="n">
         <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE8" t="n">
         <v>1.7</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
         <v>1.25</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.24</v>
+        <v>3.95</v>
       </c>
       <c r="M10" t="n">
-        <v>6.5</v>
+        <v>3.85</v>
       </c>
       <c r="N10" t="n">
-        <v>8.960000000000001</v>
+        <v>1.61</v>
       </c>
       <c r="O10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1733,13 +1733,13 @@
         <v>2.45</v>
       </c>
       <c r="M11" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="N11" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="O11" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
         <v>1.71</v>
@@ -1757,10 +1757,10 @@
         <v>4.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="V11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W11" t="n">
         <v>1.02</v>
@@ -1769,28 +1769,28 @@
         <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AA11" t="n">
         <v>2.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.2</v>
+        <v>6.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AE11" t="n">
         <v>2.32</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AG11" t="n">
         <v>1.37</v>
@@ -1858,40 +1858,40 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA12" t="n">
         <v>3</v>
@@ -1900,22 +1900,22 @@
         <v>1.36</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46058.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.65</v>
+        <v>3.7</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>4.79</v>
+        <v>1.74</v>
       </c>
       <c r="O14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC15" t="n">
         <v>3.7</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2325,25 +2325,25 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
         <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
         <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="Q16" t="n">
         <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S16" t="n">
         <v>3.58</v>
@@ -2367,16 +2367,16 @@
         <v>1.11</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.55</v>
+        <v>5.99</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.63</v>
+        <v>2.76</v>
       </c>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AD16" t="n">
         <v>1.71</v>
@@ -2388,10 +2388,10 @@
         <v>2.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46058.57291666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O17" t="n">
-        <v>10</v>
+        <v>1.53</v>
       </c>
       <c r="P17" t="n">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.41</v>
+        <v>8</v>
       </c>
       <c r="R17" t="n">
         <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="T17" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="U17" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="V17" t="n">
-        <v>3.96</v>
+        <v>4.15</v>
       </c>
       <c r="W17" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.25</v>
+        <v>5.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.02</v>
+        <v>4.4</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.53</v>
+        <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>2.83</v>
+        <v>3.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>8</v>
+        <v>1.41</v>
       </c>
       <c r="R18" t="n">
         <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="T18" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="U18" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="V18" t="n">
-        <v>4.15</v>
+        <v>3.96</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.8</v>
+        <v>6.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.4</v>
+        <v>1.02</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="M19" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>2.39</v>
       </c>
       <c r="P19" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.62</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="S19" t="n">
-        <v>1.98</v>
+        <v>2.55</v>
       </c>
       <c r="T19" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="U19" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="V19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.69</v>
+        <v>1.42</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.14</v>
+        <v>2.65</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.04</v>
+        <v>2.24</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AC19" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.42</v>
+        <v>1.9</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46058.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.75</v>
+        <v>2.55</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
-        <v>2.44</v>
+        <v>3.57</v>
       </c>
       <c r="P20" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.76</v>
+        <v>4.5</v>
       </c>
       <c r="R20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V20" t="n">
+        <v>11</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.45</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.9</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46058.625</v>
@@ -2920,16 +2920,16 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>3.54</v>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>5.21</v>
       </c>
       <c r="O21" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="P21" t="n">
         <v>2</v>
@@ -2938,22 +2938,22 @@
         <v>4.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="T21" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="U21" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V21" t="n">
         <v>8.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
@@ -2962,19 +2962,19 @@
         <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE21" t="n">
         <v>1.95</v>
@@ -2983,10 +2983,10 @@
         <v>1.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46058.64583333334</v>
@@ -3039,16 +3039,16 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="O22" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P22" t="n">
         <v>2.15</v>
@@ -3063,25 +3063,25 @@
         <v>2.69</v>
       </c>
       <c r="T22" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="U22" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V22" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="W22" t="n">
         <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
         <v>1.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA22" t="n">
         <v>2.02</v>
@@ -3090,13 +3090,13 @@
         <v>1.75</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AF22" t="n">
         <v>1.95</v>
@@ -3105,7 +3105,7 @@
         <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46058.70902777778</v>
@@ -3158,22 +3158,22 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="M23" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
         <v>3.4</v>
       </c>
       <c r="O23" t="n">
-        <v>2.8</v>
+        <v>2.57</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="R23" t="n">
         <v>1.46</v>
@@ -3182,7 +3182,7 @@
         <v>2.53</v>
       </c>
       <c r="T23" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="U23" t="n">
         <v>1.36</v>
@@ -3200,10 +3200,10 @@
         <v>1.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AA23" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB23" t="n">
         <v>1.8</v>
@@ -3215,16 +3215,16 @@
         <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46058.79166666666</v>
@@ -3277,49 +3277,49 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="M24" t="n">
-        <v>3.67</v>
+        <v>3.55</v>
       </c>
       <c r="N24" t="n">
-        <v>6.2</v>
+        <v>4.95</v>
       </c>
       <c r="O24" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="P24" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
         <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>2.98</v>
+        <v>2.69</v>
       </c>
       <c r="T24" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="U24" t="n">
         <v>1.38</v>
       </c>
       <c r="V24" t="n">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AA24" t="n">
         <v>1.95</v>
@@ -3328,7 +3328,7 @@
         <v>1.85</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AD24" t="n">
         <v>1.29</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3881,22 +3881,22 @@
         <v>6.9</v>
       </c>
       <c r="O29" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="P29" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
         <v>6.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
         <v>2.69</v>
       </c>
       <c r="T29" t="n">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="U29" t="n">
         <v>1.37</v>
@@ -3911,13 +3911,13 @@
         <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AB29" t="n">
         <v>1.8</v>
@@ -3929,16 +3929,16 @@
         <v>1.25</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46058.89583333334</v>

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46058.375</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46058.375</v>
@@ -1052,7 +1052,7 @@
         <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y5" t="n">
         <v>1.63</v>
@@ -1079,7 +1079,7 @@
         <v>1.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AH5" t="n">
         <v>1.59</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.14</v>
+        <v>3.95</v>
       </c>
       <c r="M9" t="n">
-        <v>6.4</v>
+        <v>3.85</v>
       </c>
       <c r="N9" t="n">
-        <v>9.5</v>
+        <v>1.61</v>
       </c>
       <c r="O9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.95</v>
+        <v>1.14</v>
       </c>
       <c r="M10" t="n">
-        <v>3.85</v>
+        <v>6.4</v>
       </c>
       <c r="N10" t="n">
-        <v>1.61</v>
+        <v>9.5</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>2.83</v>
       </c>
       <c r="P11" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="R11" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="S11" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="T11" t="n">
-        <v>4.2</v>
+        <v>3.58</v>
       </c>
       <c r="U11" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="V11" t="n">
-        <v>11</v>
+        <v>9.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.25</v>
+        <v>5.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AF11" t="n">
         <v>1.57</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46058.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O12" t="n">
-        <v>2.82</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="S12" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="T12" t="n">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="V12" t="n">
-        <v>9.1</v>
+        <v>11</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AA12" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.2</v>
+        <v>6.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46058.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC14" t="n">
         <v>3.7</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.68</v>
+        <v>3.7</v>
       </c>
       <c r="M15" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>4.1</v>
+        <v>1.74</v>
       </c>
       <c r="O15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46058.54166666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="M3" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="N3" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="O3" t="n">
         <v>3.02</v>
@@ -802,7 +802,7 @@
         <v>2.15</v>
       </c>
       <c r="T3" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="U3" t="n">
         <v>1.2</v>
@@ -826,19 +826,19 @@
         <v>2.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AC3" t="n">
         <v>4.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG3" t="n">
         <v>1.33</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1016,28 +1016,28 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="N5" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P5" t="n">
         <v>1.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.18</v>
+        <v>4.85</v>
       </c>
       <c r="R5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S5" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="T5" t="n">
         <v>3.92</v>
@@ -1055,10 +1055,10 @@
         <v>1.12</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AA5" t="n">
         <v>3</v>
@@ -1742,10 +1742,10 @@
         <v>2.83</v>
       </c>
       <c r="P11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="R11" t="n">
         <v>1.59</v>
@@ -1754,10 +1754,10 @@
         <v>2.18</v>
       </c>
       <c r="T11" t="n">
-        <v>3.58</v>
+        <v>3.72</v>
       </c>
       <c r="U11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="V11" t="n">
         <v>9.1</v>
@@ -1775,22 +1775,22 @@
         <v>2.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="AB11" t="n">
         <v>1.38</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.15</v>
+        <v>5.3</v>
       </c>
       <c r="AD11" t="n">
         <v>1.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG11" t="n">
         <v>1.32</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.68</v>
+        <v>3.7</v>
       </c>
       <c r="M14" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>4.1</v>
+        <v>1.74</v>
       </c>
       <c r="O14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC15" t="n">
         <v>3.7</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2920,31 +2920,31 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="M21" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>5.21</v>
+        <v>4.25</v>
       </c>
       <c r="O21" t="n">
         <v>2.3</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Q21" t="n">
         <v>4.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S21" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="T21" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U21" t="n">
         <v>1.36</v>
@@ -2953,34 +2953,34 @@
         <v>8.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z21" t="n">
         <v>2.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AC21" t="n">
-        <v>4</v>
+        <v>3.52</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG21" t="n">
         <v>1.3</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G27" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.25</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
-        <v>2.72</v>
+        <v>3.85</v>
       </c>
       <c r="N3" t="n">
-        <v>3.3</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46058.375</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="M4" t="n">
-        <v>3.85</v>
+        <v>2.7</v>
       </c>
       <c r="N4" t="n">
-        <v>8.550000000000001</v>
+        <v>3.4</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46058.375</v>
@@ -1016,34 +1016,34 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="M5" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="N5" t="n">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="O5" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="S5" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="T5" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="V5" t="n">
         <v>9.9</v>
@@ -1052,37 +1052,37 @@
         <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AA5" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG5" t="n">
         <v>1.35</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46058.41666666666</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
         <v>3.75</v>
       </c>
       <c r="N8" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="O8" t="n">
         <v>4.6</v>
@@ -1391,7 +1391,7 @@
         <v>2.25</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
         <v>2.96</v>
@@ -1403,7 +1403,7 @@
         <v>1.43</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="W8" t="n">
         <v>1.1</v>
@@ -1412,16 +1412,16 @@
         <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC8" t="n">
         <v>2.8</v>
@@ -1433,13 +1433,13 @@
         <v>1.7</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG8" t="n">
         <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46058.45833333334</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1614,10 +1614,10 @@
         <v>1.14</v>
       </c>
       <c r="M10" t="n">
-        <v>6.4</v>
+        <v>5.75</v>
       </c>
       <c r="N10" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="O10" t="n">
         <v>1.53</v>
@@ -1626,10 +1626,10 @@
         <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="S10" t="n">
         <v>4.3</v>
@@ -1650,22 +1650,22 @@
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AB10" t="n">
         <v>3.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE10" t="n">
         <v>1.53</v>
@@ -1677,7 +1677,7 @@
         <v>1.13</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1739,64 +1739,64 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46058.5</v>
@@ -1986,16 +1986,16 @@
         <v>4.68</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="T13" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="U13" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V13" t="n">
         <v>6.5</v>
@@ -2004,28 +2004,28 @@
         <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
         <v>1.95</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AF13" t="n">
         <v>1.91</v>
@@ -2034,7 +2034,7 @@
         <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46058.51388888889</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC14" t="n">
         <v>3.7</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.68</v>
+        <v>3.7</v>
       </c>
       <c r="M15" t="n">
-        <v>3.54</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>5.06</v>
+        <v>1.74</v>
       </c>
       <c r="O15" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N16" t="n">
         <v>2.5</v>
@@ -2337,7 +2337,7 @@
         <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="Q16" t="n">
         <v>3</v>
@@ -2349,7 +2349,7 @@
         <v>3.58</v>
       </c>
       <c r="T16" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="U16" t="n">
         <v>1.67</v>
@@ -2367,19 +2367,19 @@
         <v>1.11</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.99</v>
+        <v>5.75</v>
       </c>
       <c r="AA16" t="n">
         <v>1.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AE16" t="n">
         <v>1.36</v>
@@ -2388,10 +2388,10 @@
         <v>2.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46058.57291666666</v>
@@ -2444,58 +2444,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="M17" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="N17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="O17" t="n">
         <v>1.53</v>
       </c>
       <c r="P17" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="Q17" t="n">
         <v>8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>3.95</v>
+        <v>3.84</v>
       </c>
       <c r="T17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="U17" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="V17" t="n">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AD17" t="n">
         <v>1.78</v>
@@ -2507,10 +2507,10 @@
         <v>1.83</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2575,28 +2575,28 @@
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="U18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V18" t="n">
-        <v>3.96</v>
+        <v>4.05</v>
       </c>
       <c r="W18" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
@@ -2605,22 +2605,22 @@
         <v>1.06</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AE18" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AF18" t="n">
         <v>1.73</v>
@@ -2629,7 +2629,7 @@
         <v>1.08</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.76</v>
+        <v>2.55</v>
       </c>
       <c r="M19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N19" t="n">
         <v>3.2</v>
       </c>
-      <c r="N19" t="n">
-        <v>4.8</v>
-      </c>
       <c r="O19" t="n">
-        <v>2.39</v>
+        <v>3.57</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="R19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V19" t="n">
+        <v>11</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.45</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V19" t="n">
-        <v>9</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.9</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46058.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S20" t="n">
         <v>2.55</v>
       </c>
-      <c r="M20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.97</v>
-      </c>
       <c r="T20" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="U20" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.11</v>
       </c>
-      <c r="Y20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.45</v>
+        <v>1.9</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46058.625</v>
@@ -2920,19 +2920,19 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="O21" t="n">
         <v>2.3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="Q21" t="n">
         <v>4.8</v>
@@ -2941,7 +2941,7 @@
         <v>1.39</v>
       </c>
       <c r="S21" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="T21" t="n">
         <v>2.75</v>
@@ -2950,31 +2950,31 @@
         <v>1.36</v>
       </c>
       <c r="V21" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
         <v>1.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="AA21" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE21" t="n">
         <v>1.85</v>
@@ -3158,22 +3158,22 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="N23" t="n">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="O23" t="n">
         <v>2.57</v>
       </c>
       <c r="P23" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="R23" t="n">
         <v>1.46</v>
@@ -3194,19 +3194,19 @@
         <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
         <v>1.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA23" t="n">
         <v>2.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC23" t="n">
         <v>3.24</v>
@@ -3215,13 +3215,13 @@
         <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
         <v>1.7</v>
@@ -3277,16 +3277,16 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="M24" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>4.95</v>
+        <v>5.9</v>
       </c>
       <c r="O24" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="P24" t="n">
         <v>2.2</v>
@@ -3295,25 +3295,25 @@
         <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S24" t="n">
         <v>2.69</v>
       </c>
       <c r="T24" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="U24" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
         <v>1.28</v>
@@ -3322,7 +3322,7 @@
         <v>3.55</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB24" t="n">
         <v>1.85</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3872,25 +3872,25 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="M29" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="O29" t="n">
         <v>2</v>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q29" t="n">
         <v>6.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S29" t="n">
         <v>2.69</v>
@@ -3908,19 +3908,19 @@
         <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z29" t="n">
         <v>3.27</v>
       </c>
       <c r="AA29" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC29" t="n">
         <v>3.5</v>
@@ -3935,10 +3935,10 @@
         <v>1.67</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46058.89583333334</v>

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="M4" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="N4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
         <v>3.1</v>
@@ -915,10 +915,10 @@
         <v>4.63</v>
       </c>
       <c r="R4" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="S4" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="T4" t="n">
         <v>3.9</v>
@@ -930,7 +930,7 @@
         <v>10</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
         <v>1.1</v>
@@ -942,7 +942,7 @@
         <v>2.12</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="AB4" t="n">
         <v>1.33</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="N5" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="O5" t="n">
         <v>2.9</v>
@@ -1034,10 +1034,10 @@
         <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S5" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="T5" t="n">
         <v>4</v>
@@ -1067,10 +1067,10 @@
         <v>1.31</v>
       </c>
       <c r="AC5" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AE5" t="n">
         <v>2.41</v>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="M8" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
         <v>1.66</v>
@@ -1400,10 +1400,10 @@
         <v>2.53</v>
       </c>
       <c r="U8" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="V8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
         <v>1.1</v>
@@ -1427,7 +1427,7 @@
         <v>2.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
         <v>1.7</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.95</v>
+        <v>1.14</v>
       </c>
       <c r="M9" t="n">
-        <v>3.85</v>
+        <v>5.75</v>
       </c>
       <c r="N9" t="n">
-        <v>1.61</v>
+        <v>8</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.14</v>
+        <v>3.95</v>
       </c>
       <c r="M10" t="n">
-        <v>5.75</v>
+        <v>3.85</v>
       </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>1.61</v>
       </c>
       <c r="O10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1739,64 +1739,64 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46058.5</v>
@@ -1849,28 +1849,28 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.45</v>
+        <v>2.83</v>
       </c>
       <c r="M12" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="N12" t="n">
         <v>2.95</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S12" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="T12" t="n">
         <v>4.2</v>
@@ -1885,22 +1885,22 @@
         <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.25</v>
+        <v>6.3</v>
       </c>
       <c r="AD12" t="n">
         <v>1.11</v>
@@ -1912,10 +1912,10 @@
         <v>1.57</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46058.5</v>
@@ -2016,7 +2016,7 @@
         <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
         <v>3</v>
@@ -2025,7 +2025,7 @@
         <v>1.31</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
         <v>1.91</v>
@@ -2087,16 +2087,16 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="M14" t="n">
         <v>3.54</v>
       </c>
       <c r="N14" t="n">
-        <v>5.06</v>
+        <v>4.1</v>
       </c>
       <c r="O14" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="P14" t="n">
         <v>2.15</v>
@@ -2117,19 +2117,19 @@
         <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="W14" t="n">
         <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA14" t="n">
         <v>1.99</v>
@@ -2144,16 +2144,16 @@
         <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
         <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.53</v>
+        <v>10.3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.81</v>
+        <v>3.18</v>
       </c>
       <c r="Q17" t="n">
-        <v>8</v>
+        <v>1.44</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>3.84</v>
+        <v>4.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="U17" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="V17" t="n">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.08</v>
       </c>
-      <c r="Z17" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AH17" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O18" t="n">
-        <v>10</v>
+        <v>1.53</v>
       </c>
       <c r="P18" t="n">
-        <v>3.18</v>
+        <v>2.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.44</v>
+        <v>7.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="S18" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V18" t="n">
         <v>4.3</v>
       </c>
-      <c r="T18" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4.05</v>
-      </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AA18" t="n">
         <v>1.38</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AC18" t="n">
         <v>2.03</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.03</v>
+        <v>4.41</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="M19" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>3.57</v>
+        <v>2.4</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="S19" t="n">
-        <v>1.97</v>
+        <v>2.31</v>
       </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="U19" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="V19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.13</v>
+        <v>2.69</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.1</v>
+        <v>2.21</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>6.45</v>
+        <v>4.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46058.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.76</v>
+        <v>2.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>2.58</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>3.11</v>
       </c>
       <c r="O20" t="n">
-        <v>2.39</v>
+        <v>3.52</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>4.19</v>
       </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="S20" t="n">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="T20" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="V20" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.42</v>
+        <v>1.66</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.65</v>
+        <v>2.12</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.24</v>
+        <v>3.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.9</v>
+        <v>1.41</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46058.625</v>
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="M21" t="n">
         <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="O21" t="n">
         <v>2.3</v>
@@ -2935,16 +2935,16 @@
         <v>2.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S21" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="T21" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="U21" t="n">
         <v>1.36</v>
@@ -2962,19 +2962,19 @@
         <v>1.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AA21" t="n">
         <v>1.96</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE21" t="n">
         <v>1.85</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI29"/>
+  <dimension ref="A1:AI30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -655,7 +655,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -668,40 +668,40 @@
         <v>2.63</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA2" t="n">
         <v>3.5</v>
@@ -710,22 +710,22 @@
         <v>1.28</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46058.29166666666</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,19 +752,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -774,77 +774,77 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.36</v>
+        <v>2.45</v>
       </c>
       <c r="M3" t="n">
-        <v>3.85</v>
+        <v>2.62</v>
       </c>
       <c r="N3" t="n">
-        <v>8.550000000000001</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46058.375</v>
@@ -856,12 +856,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,76 +897,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.28</v>
+        <v>1.78</v>
       </c>
       <c r="M4" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.63</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="S4" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="T4" t="n">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="U4" t="n">
         <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W4" t="n">
         <v>1.03</v>
       </c>
       <c r="X4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.1</v>
       </c>
-      <c r="Y4" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AE4" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.49</v>
+        <v>1.95</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>46058.375</v>
+        <v>46058.41666666666</v>
       </c>
     </row>
     <row r="5">
@@ -1022,67 +1022,67 @@
         <v>2.5</v>
       </c>
       <c r="N5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P5" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="S5" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="U5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="V5" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Y5" t="n">
         <v>1.67</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46058.41666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.6</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>4.65</v>
       </c>
       <c r="N6" t="n">
-        <v>1.75</v>
+        <v>7.6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46058.43402777778</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.35</v>
+        <v>3.65</v>
       </c>
       <c r="M7" t="n">
-        <v>4.35</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>6.1</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46058.43402777778</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="O8" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
         <v>2.25</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="T8" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="U8" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="W8" t="n">
         <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="AD8" t="n">
         <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46058.45833333334</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="M9" t="n">
-        <v>5.75</v>
+        <v>6.4</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.3</v>
+        <v>7.19</v>
       </c>
       <c r="R9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S9" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="T9" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="U9" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="V9" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="AG9" t="n">
         <v>1.13</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>4</v>
+      </c>
+      <c r="M10" t="n">
         <v>3.95</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.85</v>
-      </c>
       <c r="N10" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O11" t="n">
-        <v>3.14</v>
+        <v>3.72</v>
       </c>
       <c r="P11" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="R11" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S11" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="T11" t="n">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="U11" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="V11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
         <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.55</v>
+        <v>6</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.49</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46058.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.83</v>
+        <v>2.65</v>
       </c>
       <c r="M12" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="N12" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="P12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="R12" t="n">
         <v>1.72</v>
       </c>
-      <c r="Q12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.67</v>
-      </c>
       <c r="S12" t="n">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="T12" t="n">
-        <v>4.2</v>
+        <v>3.94</v>
       </c>
       <c r="U12" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="V12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.3</v>
+        <v>5.65</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46058.5</v>
@@ -1977,52 +1977,52 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="P13" t="n">
         <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.68</v>
+        <v>4.31</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>2.82</v>
+        <v>2.93</v>
       </c>
       <c r="T13" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V13" t="n">
         <v>6.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AA13" t="n">
         <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE13" t="n">
         <v>1.75</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="M14" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="O14" t="n">
         <v>2.25</v>
@@ -2102,7 +2102,7 @@
         <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="R14" t="n">
         <v>1.38</v>
@@ -2111,34 +2111,34 @@
         <v>2.69</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="U14" t="n">
         <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
         <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="AD14" t="n">
         <v>1.25</v>
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="N15" t="n">
         <v>1.74</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2328,34 +2328,34 @@
         <v>2.15</v>
       </c>
       <c r="M16" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="O16" t="n">
         <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>3.32</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S16" t="n">
         <v>3.58</v>
       </c>
       <c r="T16" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U16" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="V16" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="W16" t="n">
         <v>1.14</v>
@@ -2364,28 +2364,28 @@
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AG16" t="n">
         <v>1.25</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="O17" t="n">
-        <v>10.3</v>
+        <v>1.6</v>
       </c>
       <c r="P17" t="n">
-        <v>3.18</v>
+        <v>2.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.44</v>
+        <v>7.72</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>4.3</v>
+        <v>3.72</v>
       </c>
       <c r="T17" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="V17" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="Z17" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.53</v>
+        <v>9.9</v>
       </c>
       <c r="P18" t="n">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.5</v>
+        <v>1.44</v>
       </c>
       <c r="R18" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="S18" t="n">
-        <v>3.78</v>
+        <v>4.4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="U18" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V18" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z18" t="n">
         <v>5.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.41</v>
+        <v>1.04</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>2.79</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>2.73</v>
       </c>
       <c r="O19" t="n">
-        <v>2.4</v>
+        <v>3.66</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.5</v>
+        <v>3.96</v>
       </c>
       <c r="R19" t="n">
-        <v>1.48</v>
+        <v>1.69</v>
       </c>
       <c r="S19" t="n">
-        <v>2.31</v>
+        <v>2.04</v>
       </c>
       <c r="T19" t="n">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="U19" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="V19" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.69</v>
+        <v>2.16</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.21</v>
+        <v>2.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.1</v>
+        <v>1.39</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.95</v>
+        <v>1.37</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46058.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="M20" t="n">
-        <v>2.58</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.11</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>3.52</v>
+        <v>2.44</v>
       </c>
       <c r="P20" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.19</v>
+        <v>6.45</v>
       </c>
       <c r="R20" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="S20" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="T20" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="V20" t="n">
-        <v>13</v>
+        <v>8.9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.1</v>
+        <v>2.43</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC20" t="n">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AG20" t="n">
         <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.41</v>
+        <v>1.92</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46058.625</v>
@@ -2920,58 +2920,58 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="P21" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S21" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="T21" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="U21" t="n">
         <v>1.36</v>
       </c>
       <c r="V21" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="W21" t="n">
         <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB21" t="n">
         <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="AD21" t="n">
         <v>1.29</v>
@@ -2983,10 +2983,10 @@
         <v>1.85</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46058.64583333334</v>
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,80 +3035,80 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.15</v>
+        <v>1.43</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>3.94</v>
       </c>
       <c r="N22" t="n">
-        <v>1.91</v>
+        <v>6.73</v>
       </c>
       <c r="O22" t="n">
-        <v>3.65</v>
+        <v>1.99</v>
       </c>
       <c r="P22" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.63</v>
+        <v>6.71</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="T22" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="U22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V22" t="n">
+        <v>5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.36</v>
       </c>
-      <c r="V22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.31</v>
+        <v>2.46</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46058.70902777778</v>
+        <v>46058.70833333334</v>
       </c>
     </row>
     <row r="23">
@@ -3117,27 +3117,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,76 +3158,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.19</v>
+        <v>2.95</v>
       </c>
       <c r="M23" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>3.68</v>
+        <v>2.25</v>
       </c>
       <c r="O23" t="n">
-        <v>2.57</v>
+        <v>3.5</v>
       </c>
       <c r="P23" t="n">
         <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="T23" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="U23" t="n">
         <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="W23" t="n">
         <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y23" t="n">
         <v>1.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="AD23" t="n">
         <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG23" t="n">
         <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46058.79166666666</v>
+        <v>46058.70902777778</v>
       </c>
     </row>
     <row r="24">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,37 +3277,37 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="N24" t="n">
-        <v>5.9</v>
+        <v>3.25</v>
       </c>
       <c r="O24" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="S24" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="T24" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V24" t="n">
-        <v>6.9</v>
+        <v>6.75</v>
       </c>
       <c r="W24" t="n">
         <v>1.04</v>
@@ -3316,37 +3316,37 @@
         <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46058.83333333334</v>
+        <v>46058.79166666666</v>
       </c>
     </row>
     <row r="25">
@@ -3355,27 +3355,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,76 +3396,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46058.875</v>
+        <v>46058.83333333334</v>
       </c>
     </row>
     <row r="26">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3831,116 +3831,235 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>USM Alger</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Paradou AC</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3" t="n">
+        <v>46058.875</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Cruzeiro</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="inlineStr">
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L29" t="n">
+      <c r="L30" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M30" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="N30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="R30" t="n">
         <v>1.4</v>
       </c>
-      <c r="M29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>7</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U29" t="n">
+      <c r="S30" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U30" t="n">
         <v>1.37</v>
       </c>
-      <c r="V29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W29" t="n">
+      <c r="V30" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="W30" t="n">
         <v>1.05</v>
       </c>
-      <c r="X29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y29" t="n">
+      <c r="X30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y30" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z29" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE29" t="n">
+      <c r="Z30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE30" t="n">
         <v>2.1</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AF30" t="n">
         <v>1.67</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AG30" t="n">
         <v>1.22</v>
       </c>
-      <c r="AH29" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AI29" s="3" t="n">
+      <c r="AH30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AI30" s="3" t="n">
         <v>46058.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="N4" t="n">
-        <v>5.25</v>
+        <v>3.75</v>
       </c>
       <c r="O4" t="n">
-        <v>2.38</v>
+        <v>2.95</v>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="R4" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="T4" t="n">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="V4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W4" t="n">
         <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG4" t="n">
         <v>1.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46058.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,99 +990,99 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>6</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S5" t="n">
         <v>2.1</v>
       </c>
-      <c r="M5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.02</v>
-      </c>
       <c r="T5" t="n">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="U5" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W5" t="n">
         <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC5" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG5" t="n">
         <v>1.36</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.59</v>
+        <v>1.95</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46058.41666666666</v>
@@ -1118,39 +1118,39 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
-        <v>4.65</v>
+        <v>4.33</v>
       </c>
       <c r="N6" t="n">
-        <v>7.6</v>
+        <v>6.42</v>
       </c>
       <c r="O6" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="P6" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.5</v>
+        <v>5.03</v>
       </c>
       <c r="R6" t="n">
         <v>1.3</v>
@@ -1159,49 +1159,49 @@
         <v>3.08</v>
       </c>
       <c r="T6" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="U6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V6" t="n">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="W6" t="n">
         <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z6" t="n">
         <v>4.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AE6" t="n">
         <v>1.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46058.43402777778</v>
@@ -1237,78 +1237,78 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="M7" t="n">
         <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="O7" t="n">
-        <v>4.5</v>
+        <v>4.12</v>
       </c>
       <c r="P7" t="n">
         <v>2.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="S7" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="T7" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="U7" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="V7" t="n">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
         <v>1.57</v>
@@ -1356,20 +1356,20 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.23</v>
+        <v>3.9</v>
       </c>
       <c r="M9" t="n">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
+        <v>1.68</v>
       </c>
       <c r="O9" t="n">
-        <v>1.62</v>
+        <v>4.6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.9</v>
+        <v>2.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.19</v>
+        <v>2.31</v>
       </c>
       <c r="R9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.16</v>
       </c>
-      <c r="S9" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V9" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Z9" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.28</v>
+        <v>1.58</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.25</v>
+        <v>2.12</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AE9" t="n">
         <v>1.62</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4</v>
+        <v>1.27</v>
       </c>
       <c r="M10" t="n">
-        <v>3.95</v>
+        <v>5.45</v>
       </c>
       <c r="N10" t="n">
-        <v>1.68</v>
+        <v>7.75</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46058.48958333334</v>
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N14" t="n">
-        <v>4.15</v>
+        <v>5.06</v>
       </c>
       <c r="O14" t="n">
         <v>2.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.4</v>
+        <v>4.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="T14" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
-        <v>6.8</v>
+        <v>6.95</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
         <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
         <v>3.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="AD14" t="n">
         <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AF14" t="n">
         <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2206,22 +2206,22 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="M15" t="n">
         <v>3.5</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.44</v>
-      </c>
       <c r="N15" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="O15" t="n">
         <v>4.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="R15" t="n">
         <v>1.33</v>
@@ -2230,37 +2230,37 @@
         <v>2.91</v>
       </c>
       <c r="T15" t="n">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="U15" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="V15" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
         <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z15" t="n">
         <v>3.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.87</v>
+        <v>2.97</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
         <v>1.67</v>
@@ -2272,7 +2272,7 @@
         <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2325,22 +2325,22 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="M16" t="n">
         <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="O16" t="n">
         <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.32</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
         <v>1.21</v>
@@ -2349,7 +2349,7 @@
         <v>3.58</v>
       </c>
       <c r="T16" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
         <v>1.65</v>
@@ -2364,28 +2364,28 @@
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z16" t="n">
         <v>5.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD16" t="n">
         <v>1.67</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AG16" t="n">
         <v>1.25</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.6</v>
+        <v>9.9</v>
       </c>
       <c r="P17" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.72</v>
+        <v>1.44</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="S17" t="n">
-        <v>3.72</v>
+        <v>4.4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="U17" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="V17" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AH17" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="O18" t="n">
-        <v>9.9</v>
+        <v>1.6</v>
       </c>
       <c r="P18" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.44</v>
+        <v>7.72</v>
       </c>
       <c r="R18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.14</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.16</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.11</v>
       </c>
-      <c r="Z18" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,61 +2682,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="M19" t="n">
-        <v>2.79</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.73</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>3.66</v>
+        <v>2.44</v>
       </c>
       <c r="P19" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.96</v>
+        <v>6.45</v>
       </c>
       <c r="R19" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="S19" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="T19" t="n">
-        <v>4.15</v>
+        <v>3.25</v>
       </c>
       <c r="U19" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="V19" t="n">
-        <v>13</v>
+        <v>8.9</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.9</v>
+        <v>2.43</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AC19" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AE19" t="n">
         <v>2.28</v>
@@ -2745,10 +2745,10 @@
         <v>1.55</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.37</v>
+        <v>1.92</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46058.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,61 +2801,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>2.79</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>2.73</v>
       </c>
       <c r="O20" t="n">
-        <v>2.44</v>
+        <v>3.66</v>
       </c>
       <c r="P20" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.45</v>
+        <v>3.96</v>
       </c>
       <c r="R20" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="S20" t="n">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="T20" t="n">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="U20" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="V20" t="n">
-        <v>8.9</v>
+        <v>13</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.44</v>
+        <v>2.16</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.43</v>
+        <v>2.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AE20" t="n">
         <v>2.28</v>
@@ -2864,10 +2864,10 @@
         <v>1.55</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.92</v>
+        <v>1.37</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46058.625</v>
@@ -2920,61 +2920,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>5.78</v>
       </c>
       <c r="O21" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="P21" t="n">
         <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="T21" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="U21" t="n">
         <v>1.36</v>
       </c>
       <c r="V21" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="W21" t="n">
         <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.2</v>
+        <v>3.47</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE21" t="n">
         <v>1.85</v>
@@ -2983,10 +2983,10 @@
         <v>1.85</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46058.64583333334</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G29" t="n">

--- a/jogos_2026-02-05.xlsx
+++ b/jogos_2026-02-05.xlsx
@@ -880,20 +880,20 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1466,99 +1466,99 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V9" t="n">
         <v>3.9</v>
       </c>
-      <c r="M9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="O9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V9" t="n">
-        <v>5.25</v>
-      </c>
       <c r="W9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.1</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.16</v>
-      </c>
       <c r="Z9" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AE9" t="n">
         <v>1.62</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1585,16 +1585,16 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.27</v>
+        <v>3.9</v>
       </c>
       <c r="M10" t="n">
-        <v>5.45</v>
+        <v>3.7</v>
       </c>
       <c r="N10" t="n">
-        <v>7.75</v>
+        <v>1.68</v>
       </c>
       <c r="O10" t="n">
-        <v>1.67</v>
+        <v>4.6</v>
       </c>
       <c r="P10" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.6</v>
+        <v>2.31</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>4.2</v>
+        <v>3.08</v>
       </c>
       <c r="T10" t="n">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="V10" t="n">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.1</v>
+        <v>2.12</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.67</v>
+        <v>2.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AE10" t="n">
         <v>1.62</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46058.48958333334</v>
@@ -1713,90 +1713,90 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="M11" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="N11" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="P11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="R11" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="S11" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="T11" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="V11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W11" t="n">
         <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.88</v>
+        <v>3.09</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AC11" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AF11" t="n">
         <v>1.55</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46058.5</v>
@@ -1832,20 +1832,20 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1951,90 +1951,90 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.31</v>
+        <v>4.8</v>
       </c>
       <c r="R13" t="n">
         <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>2.93</v>
+        <v>2.85</v>
       </c>
       <c r="T13" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="U13" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="V13" t="n">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="W13" t="n">
         <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AD13" t="n">
         <v>1.29</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46058.51388888889</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,99 +2061,99 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.67</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N14" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD14" t="n">
+      <c r="AF14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>2.28</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,16 +2180,16 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -2202,77 +2202,77 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC15" t="n">
         <v>3.45</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.97</v>
-      </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.25</v>
+        <v>2.28</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46058.54166666666</v>
@@ -2308,30 +2308,30 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="M16" t="n">
         <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="O16" t="n">
         <v>2.5</v>
@@ -2349,16 +2349,16 @@
         <v>3.58</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="U16" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V16" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
         <v>1.02</v>
@@ -2373,19 +2373,19 @@
         <v>1.45</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AG16" t="n">
         <v>1.25</v>
@@ -2418,16 +2418,16 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -2440,77 +2440,77 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O17" t="n">
-        <v>9.9</v>
+        <v>1.6</v>
       </c>
       <c r="P17" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.44</v>
+        <v>7.34</v>
       </c>
       <c r="R17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W17" t="n">
         <v>1.14</v>
-      </c>
-      <c r="S17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.16</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2537,99 +2537,99 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.19</v>
+        <v>12.5</v>
       </c>
       <c r="M18" t="n">
-        <v>6.5</v>
+        <v>8.9</v>
       </c>
       <c r="N18" t="n">
-        <v>10.7</v>
+        <v>1.15</v>
       </c>
       <c r="O18" t="n">
-        <v>1.6</v>
+        <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.72</v>
+        <v>1.48</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
-        <v>3.72</v>
+        <v>4.65</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="U18" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="V18" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.11</v>
+        <v>5.05</v>
       </c>
       <c r="AH18" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46058.60416666666</v>
@@ -2665,90 +2665,90 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="P19" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.45</v>
+        <v>6.86</v>
       </c>
       <c r="R19" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="n">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="T19" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="U19" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="V19" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.7</v>
+        <v>4.81</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.92</v>
+        <v>2.24</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46058.625</v>
@@ -2787,87 +2787,87 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="M20" t="n">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="N20" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="O20" t="n">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="P20" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.96</v>
+        <v>4.1</v>
       </c>
       <c r="R20" t="n">
         <v>1.69</v>
       </c>
       <c r="S20" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="T20" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="V20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="AD20" t="n">
         <v>1.06</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46058.625</v>
@@ -2903,36 +2903,36 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>5.78</v>
+        <v>5.25</v>
       </c>
       <c r="O21" t="n">
         <v>2.05</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q21" t="n">
         <v>5.5</v>
@@ -2941,13 +2941,13 @@
         <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.75</v>
+        <v>2.98</v>
       </c>
       <c r="T21" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="U21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V21" t="n">
         <v>7</v>
@@ -2959,19 +2959,19 @@
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.47</v>
+        <v>3.41</v>
       </c>
       <c r="AD21" t="n">
         <v>1.26</v>
@@ -2983,10 +2983,10 @@
         <v>1.85</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46058.64583333334</v>
@@ -3025,87 +3025,87 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="M22" t="n">
-        <v>3.94</v>
+        <v>4.1</v>
       </c>
       <c r="N22" t="n">
-        <v>6.73</v>
+        <v>6</v>
       </c>
       <c r="O22" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="P22" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.71</v>
+        <v>6</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S22" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="U22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF22" t="n">
         <v>1.55</v>
       </c>
-      <c r="V22" t="n">
-        <v>5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AG22" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46058.70833333334</v>
@@ -3141,51 +3141,51 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O23" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P23" t="n">
         <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="T23" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
         <v>7.1</v>
@@ -3194,25 +3194,25 @@
         <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB23" t="n">
         <v>1.75</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE23" t="n">
         <v>1.75</v>
@@ -3224,7 +3224,7 @@
         <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46058.70902777778</v>
@@ -3277,61 +3277,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="M24" t="n">
         <v>3.05</v>
       </c>
       <c r="N24" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
         <v>2.8</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="T24" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V24" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="W24" t="n">
         <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE24" t="n">
         <v>1.8</v>
@@ -3340,7 +3340,7 @@
         <v>1.91</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
         <v>1.65</v>
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>5.25</v>
+        <v>6.55</v>
       </c>
       <c r="O25" t="n">
         <v>2.15</v>
@@ -3414,55 +3414,55 @@
         <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="T25" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="U25" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V25" t="n">
-        <v>6.95</v>
+        <v>6</v>
       </c>
       <c r="W25" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA25" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB25" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AC25" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46058.83333333334</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="M30" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="N30" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="O30" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="P30" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>7.1</v>
+        <v>6.4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S30" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="T30" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="U30" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="V30" t="n">
-        <v>6.65</v>
+        <v>7</v>
       </c>
       <c r="W30" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC30" t="n">
         <v>3.3</v>
       </c>
-      <c r="AA30" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AD30" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46058.89583333334</v>
